--- a/data/out/lstm_results/lstm_summary.xlsx
+++ b/data/out/lstm_results/lstm_summary.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -508,23 +508,23 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>v10_date_range_no_solar_lags</t>
+          <t>v1_original</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-2.899886608123779</v>
+        <v>-0.1806454658508301</v>
       </c>
       <c r="E2" t="n">
-        <v>186.7190856933594</v>
+        <v>353.0463562011719</v>
       </c>
       <c r="F2" t="n">
-        <v>37683.89453125</v>
+        <v>296834.8125</v>
       </c>
       <c r="G2" t="n">
-        <v>194.1233978271484</v>
+        <v>544.8255004882812</v>
       </c>
       <c r="H2" t="n">
-        <v>155.3459525108337</v>
+        <v>84.06538367271423</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -532,16 +532,16 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>13057</v>
+        <v>48168</v>
       </c>
       <c r="K2" t="n">
-        <v>10445</v>
+        <v>38534</v>
       </c>
       <c r="L2" t="n">
-        <v>2612</v>
+        <v>9634</v>
       </c>
       <c r="M2" t="n">
-        <v>83.36839890480042</v>
+        <v>293.2947287559509</v>
       </c>
     </row>
     <row r="3">
@@ -557,23 +557,23 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>v10_date_range_no_solar_lags</t>
+          <t>v1_original</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-16.05233001708984</v>
+        <v>-0.1781760454177856</v>
       </c>
       <c r="E3" t="n">
-        <v>399.1917724609375</v>
+        <v>352.9155578613281</v>
       </c>
       <c r="F3" t="n">
-        <v>164773.5625</v>
+        <v>296213.96875</v>
       </c>
       <c r="G3" t="n">
-        <v>405.923095703125</v>
+        <v>544.2554321289062</v>
       </c>
       <c r="H3" t="n">
-        <v>334.919548034668</v>
+        <v>84.41361784934998</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -581,16 +581,16 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>13057</v>
+        <v>48168</v>
       </c>
       <c r="K3" t="n">
-        <v>10445</v>
+        <v>38534</v>
       </c>
       <c r="L3" t="n">
-        <v>2612</v>
+        <v>9634</v>
       </c>
       <c r="M3" t="n">
-        <v>397.7417631149292</v>
+        <v>2357.358647108078</v>
       </c>
     </row>
     <row r="4">
@@ -606,23 +606,23 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>v10_date_range_no_solar_lags</t>
+          <t>v1_original</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-13.37862873077393</v>
+        <v>-0.1891895532608032</v>
       </c>
       <c r="E4" t="n">
-        <v>365.7026062011719</v>
+        <v>353.1304931640625</v>
       </c>
       <c r="F4" t="n">
-        <v>138938.078125</v>
+        <v>298982.9375</v>
       </c>
       <c r="G4" t="n">
-        <v>372.7439880371094</v>
+        <v>546.7933349609375</v>
       </c>
       <c r="H4" t="n">
-        <v>307.416558265686</v>
+        <v>82.83399939537048</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -630,16 +630,16 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>13057</v>
+        <v>48168</v>
       </c>
       <c r="K4" t="n">
-        <v>10445</v>
+        <v>38534</v>
       </c>
       <c r="L4" t="n">
-        <v>2612</v>
+        <v>9634</v>
       </c>
       <c r="M4" t="n">
-        <v>114.0565197467804</v>
+        <v>704.3154079914093</v>
       </c>
     </row>
     <row r="5">
@@ -655,23 +655,23 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>v10_date_range_no_solar_lags</t>
+          <t>v1_original</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-24.93133163452148</v>
+        <v>-0.1808289289474487</v>
       </c>
       <c r="E5" t="n">
-        <v>494.6268310546875</v>
+        <v>353.0560607910156</v>
       </c>
       <c r="F5" t="n">
-        <v>250569.75</v>
+        <v>296880.9375</v>
       </c>
       <c r="G5" t="n">
-        <v>500.5694274902344</v>
+        <v>544.8677978515625</v>
       </c>
       <c r="H5" t="n">
-        <v>412.8370761871338</v>
+        <v>84.03937220573425</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -679,16 +679,16 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>13057</v>
+        <v>48168</v>
       </c>
       <c r="K5" t="n">
-        <v>10445</v>
+        <v>38534</v>
       </c>
       <c r="L5" t="n">
-        <v>2612</v>
+        <v>9634</v>
       </c>
       <c r="M5" t="n">
-        <v>388.3068518638611</v>
+        <v>1375.540686130524</v>
       </c>
     </row>
     <row r="6">
@@ -704,23 +704,23 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>v10_date_range_no_solar_lags</t>
+          <t>v1_original</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.3658890128135681</v>
+        <v>0.6036452651023865</v>
       </c>
       <c r="E6" t="n">
-        <v>43.13677978515625</v>
+        <v>180.9743804931641</v>
       </c>
       <c r="F6" t="n">
-        <v>6127.29931640625</v>
+        <v>99650.4765625</v>
       </c>
       <c r="G6" t="n">
-        <v>78.27706909179688</v>
+        <v>315.6746520996094</v>
       </c>
       <c r="H6" t="n">
-        <v>47.91222810745239</v>
+        <v>123.1028199195862</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -728,16 +728,16 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>13057</v>
+        <v>48168</v>
       </c>
       <c r="K6" t="n">
-        <v>10445</v>
+        <v>38534</v>
       </c>
       <c r="L6" t="n">
-        <v>2612</v>
+        <v>9634</v>
       </c>
       <c r="M6" t="n">
-        <v>24.15070986747742</v>
+        <v>80.60291481018066</v>
       </c>
     </row>
     <row r="7">
@@ -753,40 +753,5626 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>v1_original</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-0.1811213493347168</v>
+      </c>
+      <c r="E7" t="n">
+        <v>353.071533203125</v>
+      </c>
+      <c r="F7" t="n">
+        <v>296954.46875</v>
+      </c>
+      <c r="G7" t="n">
+        <v>544.935302734375</v>
+      </c>
+      <c r="H7" t="n">
+        <v>83.99848937988281</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>trained</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>48168</v>
+      </c>
+      <c r="K7" t="n">
+        <v>38534</v>
+      </c>
+      <c r="L7" t="n">
+        <v>9634</v>
+      </c>
+      <c r="M7" t="n">
+        <v>760.332691192627</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>LSTM</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>lstm_simple</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>v1_original_lags</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.1849864721298218</v>
+      </c>
+      <c r="E8" t="n">
+        <v>353.3414001464844</v>
+      </c>
+      <c r="F8" t="n">
+        <v>298080.125</v>
+      </c>
+      <c r="G8" t="n">
+        <v>545.9671630859375</v>
+      </c>
+      <c r="H8" t="n">
+        <v>83.4636926651001</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>trained</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>48144</v>
+      </c>
+      <c r="K8" t="n">
+        <v>38515</v>
+      </c>
+      <c r="L8" t="n">
+        <v>9629</v>
+      </c>
+      <c r="M8" t="n">
+        <v>626.587984085083</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>LSTM</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>lstm_deep</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>v1_original_lags</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-0.1784746646881104</v>
+      </c>
+      <c r="E9" t="n">
+        <v>352.9970703125</v>
+      </c>
+      <c r="F9" t="n">
+        <v>296442.09375</v>
+      </c>
+      <c r="G9" t="n">
+        <v>544.4649658203125</v>
+      </c>
+      <c r="H9" t="n">
+        <v>84.37647819519043</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>trained</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>48144</v>
+      </c>
+      <c r="K9" t="n">
+        <v>38515</v>
+      </c>
+      <c r="L9" t="n">
+        <v>9629</v>
+      </c>
+      <c r="M9" t="n">
+        <v>2893.619547367096</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>LSTM</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>lstm_bidirectional</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>v1_original_lags</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>-0.1793237924575806</v>
+      </c>
+      <c r="E10" t="n">
+        <v>353.0417785644531</v>
+      </c>
+      <c r="F10" t="n">
+        <v>296655.71875</v>
+      </c>
+      <c r="G10" t="n">
+        <v>544.6611328125</v>
+      </c>
+      <c r="H10" t="n">
+        <v>84.25659537315369</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>trained</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>48144</v>
+      </c>
+      <c r="K10" t="n">
+        <v>38515</v>
+      </c>
+      <c r="L10" t="n">
+        <v>9629</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1080.268439769745</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>LSTM</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>bilstm_stacked</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>v1_original_lags</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>-0.1764931678771973</v>
+      </c>
+      <c r="E11" t="n">
+        <v>352.8927917480469</v>
+      </c>
+      <c r="F11" t="n">
+        <v>295943.65625</v>
+      </c>
+      <c r="G11" t="n">
+        <v>544.0070190429688</v>
+      </c>
+      <c r="H11" t="n">
+        <v>84.65816974639893</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>trained</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>48144</v>
+      </c>
+      <c r="K11" t="n">
+        <v>38515</v>
+      </c>
+      <c r="L11" t="n">
+        <v>9629</v>
+      </c>
+      <c r="M11" t="n">
+        <v>3267.539879083633</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>LSTM</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>cnn_lstm</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>v1_original_lags</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>0.877402126789093</v>
+      </c>
+      <c r="E12" t="n">
+        <v>82.91512298583984</v>
+      </c>
+      <c r="F12" t="n">
+        <v>30839.16015625</v>
+      </c>
+      <c r="G12" t="n">
+        <v>175.6108245849609</v>
+      </c>
+      <c r="H12" t="n">
+        <v>165.5485272407532</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>trained</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>48144</v>
+      </c>
+      <c r="K12" t="n">
+        <v>38515</v>
+      </c>
+      <c r="L12" t="n">
+        <v>9629</v>
+      </c>
+      <c r="M12" t="n">
+        <v>144.9871158599854</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>LSTM</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>attention_lstm</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>v1_original_lags</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>-0.1820282936096191</v>
+      </c>
+      <c r="E13" t="n">
+        <v>353.1844482421875</v>
+      </c>
+      <c r="F13" t="n">
+        <v>297336</v>
+      </c>
+      <c r="G13" t="n">
+        <v>545.2852172851562</v>
+      </c>
+      <c r="H13" t="n">
+        <v>83.87621641159058</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>trained</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>48144</v>
+      </c>
+      <c r="K13" t="n">
+        <v>38515</v>
+      </c>
+      <c r="L13" t="n">
+        <v>9629</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1602.445814371109</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>LSTM</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>lstm_simple</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>v2_with_calendar</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>-0.1835010051727295</v>
+      </c>
+      <c r="E14" t="n">
+        <v>353.1982116699219</v>
+      </c>
+      <c r="F14" t="n">
+        <v>297552.75</v>
+      </c>
+      <c r="G14" t="n">
+        <v>545.4839477539062</v>
+      </c>
+      <c r="H14" t="n">
+        <v>83.66596102714539</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>trained</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>48168</v>
+      </c>
+      <c r="K14" t="n">
+        <v>38534</v>
+      </c>
+      <c r="L14" t="n">
+        <v>9634</v>
+      </c>
+      <c r="M14" t="n">
+        <v>611.3740825653076</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>LSTM</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>lstm_deep</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>v2_with_calendar</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>-0.1792888641357422</v>
+      </c>
+      <c r="E15" t="n">
+        <v>352.9745178222656</v>
+      </c>
+      <c r="F15" t="n">
+        <v>296493.75</v>
+      </c>
+      <c r="G15" t="n">
+        <v>544.5123901367188</v>
+      </c>
+      <c r="H15" t="n">
+        <v>84.25635695457458</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>trained</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>48168</v>
+      </c>
+      <c r="K15" t="n">
+        <v>38534</v>
+      </c>
+      <c r="L15" t="n">
+        <v>9634</v>
+      </c>
+      <c r="M15" t="n">
+        <v>2763.323985815048</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>LSTM</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>lstm_bidirectional</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>v2_with_calendar</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>-0.1808005571365356</v>
+      </c>
+      <c r="E16" t="n">
+        <v>352.5503845214844</v>
+      </c>
+      <c r="F16" t="n">
+        <v>296873.8125</v>
+      </c>
+      <c r="G16" t="n">
+        <v>544.8612670898438</v>
+      </c>
+      <c r="H16" t="n">
+        <v>83.80505442619324</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>trained</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>48168</v>
+      </c>
+      <c r="K16" t="n">
+        <v>38534</v>
+      </c>
+      <c r="L16" t="n">
+        <v>9634</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1038.078210353851</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>LSTM</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>bilstm_stacked</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>v2_with_calendar</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>-0.1761900186538696</v>
+      </c>
+      <c r="E17" t="n">
+        <v>352.8108215332031</v>
+      </c>
+      <c r="F17" t="n">
+        <v>295714.65625</v>
+      </c>
+      <c r="G17" t="n">
+        <v>543.7965087890625</v>
+      </c>
+      <c r="H17" t="n">
+        <v>84.69585776329041</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>trained</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>48168</v>
+      </c>
+      <c r="K17" t="n">
+        <v>38534</v>
+      </c>
+      <c r="L17" t="n">
+        <v>9634</v>
+      </c>
+      <c r="M17" t="n">
+        <v>3097.08208155632</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>LSTM</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>cnn_lstm</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>v2_with_calendar</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>0.4091949462890625</v>
+      </c>
+      <c r="E18" t="n">
+        <v>226.9432525634766</v>
+      </c>
+      <c r="F18" t="n">
+        <v>148538.671875</v>
+      </c>
+      <c r="G18" t="n">
+        <v>385.4071655273438</v>
+      </c>
+      <c r="H18" t="n">
+        <v>98.91106486320496</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>trained</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>48168</v>
+      </c>
+      <c r="K18" t="n">
+        <v>38534</v>
+      </c>
+      <c r="L18" t="n">
+        <v>9634</v>
+      </c>
+      <c r="M18" t="n">
+        <v>132.9726467132568</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>LSTM</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>attention_lstm</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>v2_with_calendar</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>-0.1839427947998047</v>
+      </c>
+      <c r="E19" t="n">
+        <v>353.2218322753906</v>
+      </c>
+      <c r="F19" t="n">
+        <v>297663.8125</v>
+      </c>
+      <c r="G19" t="n">
+        <v>545.5857543945312</v>
+      </c>
+      <c r="H19" t="n">
+        <v>83.60446095466614</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>trained</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>48168</v>
+      </c>
+      <c r="K19" t="n">
+        <v>38534</v>
+      </c>
+      <c r="L19" t="n">
+        <v>9634</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1535.720843553543</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>LSTM</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>lstm_simple</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>v2_with_calendar_lags</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>-0.1815341711044312</v>
+      </c>
+      <c r="E20" t="n">
+        <v>353.1583251953125</v>
+      </c>
+      <c r="F20" t="n">
+        <v>297211.71875</v>
+      </c>
+      <c r="G20" t="n">
+        <v>545.1712646484375</v>
+      </c>
+      <c r="H20" t="n">
+        <v>83.94517302513123</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>trained</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>48144</v>
+      </c>
+      <c r="K20" t="n">
+        <v>38515</v>
+      </c>
+      <c r="L20" t="n">
+        <v>9629</v>
+      </c>
+      <c r="M20" t="n">
+        <v>599.4810788631439</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>LSTM</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>lstm_deep</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>v2_with_calendar_lags</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>-0.1791504621505737</v>
+      </c>
+      <c r="E21" t="n">
+        <v>353.0326843261719</v>
+      </c>
+      <c r="F21" t="n">
+        <v>296612.09375</v>
+      </c>
+      <c r="G21" t="n">
+        <v>544.6210327148438</v>
+      </c>
+      <c r="H21" t="n">
+        <v>84.28075313568115</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>trained</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>48144</v>
+      </c>
+      <c r="K21" t="n">
+        <v>38515</v>
+      </c>
+      <c r="L21" t="n">
+        <v>9629</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1650.376976490021</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>LSTM</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>lstm_bidirectional</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>v2_with_calendar_lags</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>-0.1649044752120972</v>
+      </c>
+      <c r="E22" t="n">
+        <v>348.7728271484375</v>
+      </c>
+      <c r="F22" t="n">
+        <v>293028.5625</v>
+      </c>
+      <c r="G22" t="n">
+        <v>541.3211059570312</v>
+      </c>
+      <c r="H22" t="n">
+        <v>84.35121178627014</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>trained</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>48144</v>
+      </c>
+      <c r="K22" t="n">
+        <v>38515</v>
+      </c>
+      <c r="L22" t="n">
+        <v>9629</v>
+      </c>
+      <c r="M22" t="n">
+        <v>432.9987087249756</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>LSTM</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>bilstm_stacked</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>v2_with_calendar_lags</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>-0.174612283706665</v>
+      </c>
+      <c r="E23" t="n">
+        <v>352.7944946289062</v>
+      </c>
+      <c r="F23" t="n">
+        <v>295470.5625</v>
+      </c>
+      <c r="G23" t="n">
+        <v>543.572021484375</v>
+      </c>
+      <c r="H23" t="n">
+        <v>84.92749333381653</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>trained</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>48144</v>
+      </c>
+      <c r="K23" t="n">
+        <v>38515</v>
+      </c>
+      <c r="L23" t="n">
+        <v>9629</v>
+      </c>
+      <c r="M23" t="n">
+        <v>3092.324020624161</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>LSTM</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>cnn_lstm</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>v2_with_calendar_lags</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>0.870366632938385</v>
+      </c>
+      <c r="E24" t="n">
+        <v>86.07351684570312</v>
+      </c>
+      <c r="F24" t="n">
+        <v>32608.923828125</v>
+      </c>
+      <c r="G24" t="n">
+        <v>180.5794067382812</v>
+      </c>
+      <c r="H24" t="n">
+        <v>164.8012399673462</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>trained</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>48144</v>
+      </c>
+      <c r="K24" t="n">
+        <v>38515</v>
+      </c>
+      <c r="L24" t="n">
+        <v>9629</v>
+      </c>
+      <c r="M24" t="n">
+        <v>139.01584815979</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>LSTM</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>attention_lstm</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>v2_with_calendar_lags</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>-0.1796610355377197</v>
+      </c>
+      <c r="E25" t="n">
+        <v>353.0595092773438</v>
+      </c>
+      <c r="F25" t="n">
+        <v>296740.53125</v>
+      </c>
+      <c r="G25" t="n">
+        <v>544.7389526367188</v>
+      </c>
+      <c r="H25" t="n">
+        <v>84.20885801315308</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>trained</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>48144</v>
+      </c>
+      <c r="K25" t="n">
+        <v>38515</v>
+      </c>
+      <c r="L25" t="n">
+        <v>9629</v>
+      </c>
+      <c r="M25" t="n">
+        <v>1658.377989292145</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>LSTM</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>lstm_simple</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>v3_no_solar</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>-0.1829816102981567</v>
+      </c>
+      <c r="E26" t="n">
+        <v>353.1705017089844</v>
+      </c>
+      <c r="F26" t="n">
+        <v>297422.15625</v>
+      </c>
+      <c r="G26" t="n">
+        <v>545.3642578125</v>
+      </c>
+      <c r="H26" t="n">
+        <v>83.73846411705017</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>trained</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
+        <v>48168</v>
+      </c>
+      <c r="K26" t="n">
+        <v>38534</v>
+      </c>
+      <c r="L26" t="n">
+        <v>9634</v>
+      </c>
+      <c r="M26" t="n">
+        <v>629.5882449150085</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>LSTM</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>lstm_deep</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>v3_no_solar</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>-0.1782444715499878</v>
+      </c>
+      <c r="E27" t="n">
+        <v>352.9192504882812</v>
+      </c>
+      <c r="F27" t="n">
+        <v>296231.15625</v>
+      </c>
+      <c r="G27" t="n">
+        <v>544.271240234375</v>
+      </c>
+      <c r="H27" t="n">
+        <v>84.4039261341095</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>trained</t>
+        </is>
+      </c>
+      <c r="J27" t="n">
+        <v>48168</v>
+      </c>
+      <c r="K27" t="n">
+        <v>38534</v>
+      </c>
+      <c r="L27" t="n">
+        <v>9634</v>
+      </c>
+      <c r="M27" t="n">
+        <v>2797.92311000824</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>LSTM</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>lstm_bidirectional</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>v3_no_solar</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>-0.1815623044967651</v>
+      </c>
+      <c r="E28" t="n">
+        <v>353.0948791503906</v>
+      </c>
+      <c r="F28" t="n">
+        <v>297065.34375</v>
+      </c>
+      <c r="G28" t="n">
+        <v>545.0369873046875</v>
+      </c>
+      <c r="H28" t="n">
+        <v>83.93662571907043</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>trained</t>
+        </is>
+      </c>
+      <c r="J28" t="n">
+        <v>48168</v>
+      </c>
+      <c r="K28" t="n">
+        <v>38534</v>
+      </c>
+      <c r="L28" t="n">
+        <v>9634</v>
+      </c>
+      <c r="M28" t="n">
+        <v>1072.595561981201</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>LSTM</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>bilstm_stacked</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>v3_no_solar</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>-0.1757632493972778</v>
+      </c>
+      <c r="E29" t="n">
+        <v>352.7883911132812</v>
+      </c>
+      <c r="F29" t="n">
+        <v>295607.34375</v>
+      </c>
+      <c r="G29" t="n">
+        <v>543.6978149414062</v>
+      </c>
+      <c r="H29" t="n">
+        <v>84.75650548934937</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>trained</t>
+        </is>
+      </c>
+      <c r="J29" t="n">
+        <v>48168</v>
+      </c>
+      <c r="K29" t="n">
+        <v>38534</v>
+      </c>
+      <c r="L29" t="n">
+        <v>9634</v>
+      </c>
+      <c r="M29" t="n">
+        <v>3215.552021503448</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>LSTM</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>cnn_lstm</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>v3_no_solar</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>0.2567023038864136</v>
+      </c>
+      <c r="E30" t="n">
+        <v>271.4600219726562</v>
+      </c>
+      <c r="F30" t="n">
+        <v>186877.984375</v>
+      </c>
+      <c r="G30" t="n">
+        <v>432.2938537597656</v>
+      </c>
+      <c r="H30" t="n">
+        <v>85.81500649452209</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>trained</t>
+        </is>
+      </c>
+      <c r="J30" t="n">
+        <v>48168</v>
+      </c>
+      <c r="K30" t="n">
+        <v>38534</v>
+      </c>
+      <c r="L30" t="n">
+        <v>9634</v>
+      </c>
+      <c r="M30" t="n">
+        <v>134.5374822616577</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>LSTM</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>attention_lstm</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>v3_no_solar</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>-0.1799216270446777</v>
+      </c>
+      <c r="E31" t="n">
+        <v>353.0079040527344</v>
+      </c>
+      <c r="F31" t="n">
+        <v>296652.8125</v>
+      </c>
+      <c r="G31" t="n">
+        <v>544.658447265625</v>
+      </c>
+      <c r="H31" t="n">
+        <v>84.16705727577209</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>trained</t>
+        </is>
+      </c>
+      <c r="J31" t="n">
+        <v>48168</v>
+      </c>
+      <c r="K31" t="n">
+        <v>38534</v>
+      </c>
+      <c r="L31" t="n">
+        <v>9634</v>
+      </c>
+      <c r="M31" t="n">
+        <v>1649.108861446381</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>LSTM</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>lstm_simple</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>v3_no_solar_lags</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>-0.1827964782714844</v>
+      </c>
+      <c r="E32" t="n">
+        <v>353.2252502441406</v>
+      </c>
+      <c r="F32" t="n">
+        <v>297529.25</v>
+      </c>
+      <c r="G32" t="n">
+        <v>545.46240234375</v>
+      </c>
+      <c r="H32" t="n">
+        <v>83.76876711845398</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>trained</t>
+        </is>
+      </c>
+      <c r="J32" t="n">
+        <v>48144</v>
+      </c>
+      <c r="K32" t="n">
+        <v>38515</v>
+      </c>
+      <c r="L32" t="n">
+        <v>9629</v>
+      </c>
+      <c r="M32" t="n">
+        <v>668.8328137397766</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>LSTM</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>lstm_deep</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>v3_no_solar_lags</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>-0.1782660484313965</v>
+      </c>
+      <c r="E33" t="n">
+        <v>352.9860534667969</v>
+      </c>
+      <c r="F33" t="n">
+        <v>296389.65625</v>
+      </c>
+      <c r="G33" t="n">
+        <v>544.4168090820312</v>
+      </c>
+      <c r="H33" t="n">
+        <v>84.40588116645813</v>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>trained</t>
+        </is>
+      </c>
+      <c r="J33" t="n">
+        <v>48144</v>
+      </c>
+      <c r="K33" t="n">
+        <v>38515</v>
+      </c>
+      <c r="L33" t="n">
+        <v>9629</v>
+      </c>
+      <c r="M33" t="n">
+        <v>2966.902260780334</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>LSTM</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>lstm_bidirectional</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>v3_no_solar_lags</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>-0.1775321960449219</v>
+      </c>
+      <c r="E34" t="n">
+        <v>351.987548828125</v>
+      </c>
+      <c r="F34" t="n">
+        <v>296205.03125</v>
+      </c>
+      <c r="G34" t="n">
+        <v>544.2471923828125</v>
+      </c>
+      <c r="H34" t="n">
+        <v>83.91743898391724</v>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>trained</t>
+        </is>
+      </c>
+      <c r="J34" t="n">
+        <v>48144</v>
+      </c>
+      <c r="K34" t="n">
+        <v>38515</v>
+      </c>
+      <c r="L34" t="n">
+        <v>9629</v>
+      </c>
+      <c r="M34" t="n">
+        <v>1130.771016597748</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>LSTM</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>bilstm_stacked</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>v3_no_solar_lags</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>-0.178025484085083</v>
+      </c>
+      <c r="E35" t="n">
+        <v>352.9733581542969</v>
+      </c>
+      <c r="F35" t="n">
+        <v>296329.09375</v>
+      </c>
+      <c r="G35" t="n">
+        <v>544.3612060546875</v>
+      </c>
+      <c r="H35" t="n">
+        <v>84.44027900695801</v>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>trained</t>
+        </is>
+      </c>
+      <c r="J35" t="n">
+        <v>48144</v>
+      </c>
+      <c r="K35" t="n">
+        <v>38515</v>
+      </c>
+      <c r="L35" t="n">
+        <v>9629</v>
+      </c>
+      <c r="M35" t="n">
+        <v>3436.718383073807</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>LSTM</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>cnn_lstm</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>v3_no_solar_lags</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>0.8736268281936646</v>
+      </c>
+      <c r="E36" t="n">
+        <v>83.25140380859375</v>
+      </c>
+      <c r="F36" t="n">
+        <v>31788.837890625</v>
+      </c>
+      <c r="G36" t="n">
+        <v>178.2942504882812</v>
+      </c>
+      <c r="H36" t="n">
+        <v>163.3793950080872</v>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>trained</t>
+        </is>
+      </c>
+      <c r="J36" t="n">
+        <v>48144</v>
+      </c>
+      <c r="K36" t="n">
+        <v>38515</v>
+      </c>
+      <c r="L36" t="n">
+        <v>9629</v>
+      </c>
+      <c r="M36" t="n">
+        <v>153.638968706131</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>LSTM</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>attention_lstm</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>v3_no_solar_lags</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>-0.1804367303848267</v>
+      </c>
+      <c r="E37" t="n">
+        <v>353.1004333496094</v>
+      </c>
+      <c r="F37" t="n">
+        <v>296935.6875</v>
+      </c>
+      <c r="G37" t="n">
+        <v>544.9180297851562</v>
+      </c>
+      <c r="H37" t="n">
+        <v>84.09969806671143</v>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>trained</t>
+        </is>
+      </c>
+      <c r="J37" t="n">
+        <v>48144</v>
+      </c>
+      <c r="K37" t="n">
+        <v>38515</v>
+      </c>
+      <c r="L37" t="n">
+        <v>9629</v>
+      </c>
+      <c r="M37" t="n">
+        <v>1771.250571250916</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>LSTM</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>lstm_simple</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>v4_no_fuel_consumption</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>-0.1822603940963745</v>
+      </c>
+      <c r="E38" t="n">
+        <v>353.1320190429688</v>
+      </c>
+      <c r="F38" t="n">
+        <v>297240.84375</v>
+      </c>
+      <c r="G38" t="n">
+        <v>545.197998046875</v>
+      </c>
+      <c r="H38" t="n">
+        <v>83.83899331092834</v>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>trained</t>
+        </is>
+      </c>
+      <c r="J38" t="n">
+        <v>48168</v>
+      </c>
+      <c r="K38" t="n">
+        <v>38534</v>
+      </c>
+      <c r="L38" t="n">
+        <v>9634</v>
+      </c>
+      <c r="M38" t="n">
+        <v>669.7014167308807</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>LSTM</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>lstm_deep</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>v4_no_fuel_consumption</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>-0.1788915395736694</v>
+      </c>
+      <c r="E39" t="n">
+        <v>352.9534606933594</v>
+      </c>
+      <c r="F39" t="n">
+        <v>296393.84375</v>
+      </c>
+      <c r="G39" t="n">
+        <v>544.420654296875</v>
+      </c>
+      <c r="H39" t="n">
+        <v>84.31215882301331</v>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>trained</t>
+        </is>
+      </c>
+      <c r="J39" t="n">
+        <v>48168</v>
+      </c>
+      <c r="K39" t="n">
+        <v>38534</v>
+      </c>
+      <c r="L39" t="n">
+        <v>9634</v>
+      </c>
+      <c r="M39" t="n">
+        <v>3078.732812404633</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>LSTM</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>lstm_bidirectional</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>v4_no_fuel_consumption</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>-0.1802815198898315</v>
+      </c>
+      <c r="E40" t="n">
+        <v>353.0270080566406</v>
+      </c>
+      <c r="F40" t="n">
+        <v>296743.3125</v>
+      </c>
+      <c r="G40" t="n">
+        <v>544.7415161132812</v>
+      </c>
+      <c r="H40" t="n">
+        <v>84.1163158416748</v>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>trained</t>
+        </is>
+      </c>
+      <c r="J40" t="n">
+        <v>48168</v>
+      </c>
+      <c r="K40" t="n">
+        <v>38534</v>
+      </c>
+      <c r="L40" t="n">
+        <v>9634</v>
+      </c>
+      <c r="M40" t="n">
+        <v>1186.081163883209</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>LSTM</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>bilstm_stacked</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>v4_no_fuel_consumption</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>-0.1775182485580444</v>
+      </c>
+      <c r="E41" t="n">
+        <v>352.8807067871094</v>
+      </c>
+      <c r="F41" t="n">
+        <v>296048.59375</v>
+      </c>
+      <c r="G41" t="n">
+        <v>544.1034545898438</v>
+      </c>
+      <c r="H41" t="n">
+        <v>84.50695276260376</v>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>trained</t>
+        </is>
+      </c>
+      <c r="J41" t="n">
+        <v>48168</v>
+      </c>
+      <c r="K41" t="n">
+        <v>38534</v>
+      </c>
+      <c r="L41" t="n">
+        <v>9634</v>
+      </c>
+      <c r="M41" t="n">
+        <v>3246.754796981812</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>LSTM</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>cnn_lstm</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>v4_no_fuel_consumption</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>0.5032433867454529</v>
+      </c>
+      <c r="E42" t="n">
+        <v>190.215576171875</v>
+      </c>
+      <c r="F42" t="n">
+        <v>124893.2578125</v>
+      </c>
+      <c r="G42" t="n">
+        <v>353.4024047851562</v>
+      </c>
+      <c r="H42" t="n">
+        <v>116.370701789856</v>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>trained</t>
+        </is>
+      </c>
+      <c r="J42" t="n">
+        <v>48168</v>
+      </c>
+      <c r="K42" t="n">
+        <v>38534</v>
+      </c>
+      <c r="L42" t="n">
+        <v>9634</v>
+      </c>
+      <c r="M42" t="n">
+        <v>141.9222481250763</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>LSTM</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>attention_lstm</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>v4_no_fuel_consumption</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>-0.1810859441757202</v>
+      </c>
+      <c r="E43" t="n">
+        <v>353.0696411132812</v>
+      </c>
+      <c r="F43" t="n">
+        <v>296945.5625</v>
+      </c>
+      <c r="G43" t="n">
+        <v>544.9271240234375</v>
+      </c>
+      <c r="H43" t="n">
+        <v>84.00328755378723</v>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>trained</t>
+        </is>
+      </c>
+      <c r="J43" t="n">
+        <v>48168</v>
+      </c>
+      <c r="K43" t="n">
+        <v>38534</v>
+      </c>
+      <c r="L43" t="n">
+        <v>9634</v>
+      </c>
+      <c r="M43" t="n">
+        <v>1731.547010421753</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>LSTM</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>lstm_simple</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>v4_no_fuel_consumption_lags</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>-0.182407021522522</v>
+      </c>
+      <c r="E44" t="n">
+        <v>353.20458984375</v>
+      </c>
+      <c r="F44" t="n">
+        <v>297431.28125</v>
+      </c>
+      <c r="G44" t="n">
+        <v>545.3726196289062</v>
+      </c>
+      <c r="H44" t="n">
+        <v>83.82297158241272</v>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>trained</t>
+        </is>
+      </c>
+      <c r="J44" t="n">
+        <v>48144</v>
+      </c>
+      <c r="K44" t="n">
+        <v>38515</v>
+      </c>
+      <c r="L44" t="n">
+        <v>9629</v>
+      </c>
+      <c r="M44" t="n">
+        <v>694.4934682846069</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>LSTM</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>lstm_deep</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>v4_no_fuel_consumption_lags</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>-0.1786317825317383</v>
+      </c>
+      <c r="E45" t="n">
+        <v>353.0053100585938</v>
+      </c>
+      <c r="F45" t="n">
+        <v>296481.625</v>
+      </c>
+      <c r="G45" t="n">
+        <v>544.5012817382812</v>
+      </c>
+      <c r="H45" t="n">
+        <v>84.35465693473816</v>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>trained</t>
+        </is>
+      </c>
+      <c r="J45" t="n">
+        <v>48144</v>
+      </c>
+      <c r="K45" t="n">
+        <v>38515</v>
+      </c>
+      <c r="L45" t="n">
+        <v>9629</v>
+      </c>
+      <c r="M45" t="n">
+        <v>2984.304391860962</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>LSTM</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>lstm_bidirectional</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>v4_no_fuel_consumption_lags</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>-0.1807327270507812</v>
+      </c>
+      <c r="E46" t="n">
+        <v>353.1160278320312</v>
+      </c>
+      <c r="F46" t="n">
+        <v>297010.125</v>
+      </c>
+      <c r="G46" t="n">
+        <v>544.986328125</v>
+      </c>
+      <c r="H46" t="n">
+        <v>84.05765891075134</v>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>trained</t>
+        </is>
+      </c>
+      <c r="J46" t="n">
+        <v>48144</v>
+      </c>
+      <c r="K46" t="n">
+        <v>38515</v>
+      </c>
+      <c r="L46" t="n">
+        <v>9629</v>
+      </c>
+      <c r="M46" t="n">
+        <v>1146.591079711914</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>LSTM</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>bilstm_stacked</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>v4_no_fuel_consumption_lags</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>-0.1779319047927856</v>
+      </c>
+      <c r="E47" t="n">
+        <v>352.9684753417969</v>
+      </c>
+      <c r="F47" t="n">
+        <v>296305.5625</v>
+      </c>
+      <c r="G47" t="n">
+        <v>544.3395385742188</v>
+      </c>
+      <c r="H47" t="n">
+        <v>84.45345759391785</v>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>trained</t>
+        </is>
+      </c>
+      <c r="J47" t="n">
+        <v>48144</v>
+      </c>
+      <c r="K47" t="n">
+        <v>38515</v>
+      </c>
+      <c r="L47" t="n">
+        <v>9629</v>
+      </c>
+      <c r="M47" t="n">
+        <v>3397.189221858978</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>LSTM</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>cnn_lstm</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>v4_no_fuel_consumption_lags</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>0.8634767532348633</v>
+      </c>
+      <c r="E48" t="n">
+        <v>93.05460357666016</v>
+      </c>
+      <c r="F48" t="n">
+        <v>34342.05859375</v>
+      </c>
+      <c r="G48" t="n">
+        <v>185.3161010742188</v>
+      </c>
+      <c r="H48" t="n">
+        <v>154.8671841621399</v>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>trained</t>
+        </is>
+      </c>
+      <c r="J48" t="n">
+        <v>48144</v>
+      </c>
+      <c r="K48" t="n">
+        <v>38515</v>
+      </c>
+      <c r="L48" t="n">
+        <v>9629</v>
+      </c>
+      <c r="M48" t="n">
+        <v>150.6552262306213</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>LSTM</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>attention_lstm</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>v4_no_fuel_consumption_lags</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>-0.1798226833343506</v>
+      </c>
+      <c r="E49" t="n">
+        <v>353.0679931640625</v>
+      </c>
+      <c r="F49" t="n">
+        <v>296781.21875</v>
+      </c>
+      <c r="G49" t="n">
+        <v>544.7763061523438</v>
+      </c>
+      <c r="H49" t="n">
+        <v>84.18624997138977</v>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>trained</t>
+        </is>
+      </c>
+      <c r="J49" t="n">
+        <v>48144</v>
+      </c>
+      <c r="K49" t="n">
+        <v>38515</v>
+      </c>
+      <c r="L49" t="n">
+        <v>9629</v>
+      </c>
+      <c r="M49" t="n">
+        <v>1715.311976671219</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>LSTM</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>lstm_simple</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>v5_no_fuel_and_cost</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>-0.1816062927246094</v>
+      </c>
+      <c r="E50" t="n">
+        <v>353.0971984863281</v>
+      </c>
+      <c r="F50" t="n">
+        <v>297076.375</v>
+      </c>
+      <c r="G50" t="n">
+        <v>545.047119140625</v>
+      </c>
+      <c r="H50" t="n">
+        <v>83.93042087554932</v>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>trained</t>
+        </is>
+      </c>
+      <c r="J50" t="n">
+        <v>48168</v>
+      </c>
+      <c r="K50" t="n">
+        <v>38534</v>
+      </c>
+      <c r="L50" t="n">
+        <v>9634</v>
+      </c>
+      <c r="M50" t="n">
+        <v>712.2305653095245</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>LSTM</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>lstm_deep</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>v5_no_fuel_and_cost</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>-0.1787408590316772</v>
+      </c>
+      <c r="E51" t="n">
+        <v>352.9454956054688</v>
+      </c>
+      <c r="F51" t="n">
+        <v>296355.96875</v>
+      </c>
+      <c r="G51" t="n">
+        <v>544.3858642578125</v>
+      </c>
+      <c r="H51" t="n">
+        <v>84.33372974395752</v>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>trained</t>
+        </is>
+      </c>
+      <c r="J51" t="n">
+        <v>48168</v>
+      </c>
+      <c r="K51" t="n">
+        <v>38534</v>
+      </c>
+      <c r="L51" t="n">
+        <v>9634</v>
+      </c>
+      <c r="M51" t="n">
+        <v>2941.575678110123</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>LSTM</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>lstm_bidirectional</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>v5_no_fuel_and_cost</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>-0.1781986951828003</v>
+      </c>
+      <c r="E52" t="n">
+        <v>352.9167785644531</v>
+      </c>
+      <c r="F52" t="n">
+        <v>296219.65625</v>
+      </c>
+      <c r="G52" t="n">
+        <v>544.2606811523438</v>
+      </c>
+      <c r="H52" t="n">
+        <v>84.41035747528076</v>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>trained</t>
+        </is>
+      </c>
+      <c r="J52" t="n">
+        <v>48168</v>
+      </c>
+      <c r="K52" t="n">
+        <v>38534</v>
+      </c>
+      <c r="L52" t="n">
+        <v>9634</v>
+      </c>
+      <c r="M52" t="n">
+        <v>382.984046459198</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>LSTM</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>bilstm_stacked</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>v5_no_fuel_and_cost</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>-0.1766026020050049</v>
+      </c>
+      <c r="E53" t="n">
+        <v>352.8324279785156</v>
+      </c>
+      <c r="F53" t="n">
+        <v>295818.375</v>
+      </c>
+      <c r="G53" t="n">
+        <v>543.8919067382812</v>
+      </c>
+      <c r="H53" t="n">
+        <v>84.63682532310486</v>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>trained</t>
+        </is>
+      </c>
+      <c r="J53" t="n">
+        <v>48168</v>
+      </c>
+      <c r="K53" t="n">
+        <v>38534</v>
+      </c>
+      <c r="L53" t="n">
+        <v>9634</v>
+      </c>
+      <c r="M53" t="n">
+        <v>2026.360802650452</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>LSTM</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>cnn_lstm</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>v5_no_fuel_and_cost</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>0.446980357170105</v>
+      </c>
+      <c r="E54" t="n">
+        <v>205.914306640625</v>
+      </c>
+      <c r="F54" t="n">
+        <v>139038.75</v>
+      </c>
+      <c r="G54" t="n">
+        <v>372.8789978027344</v>
+      </c>
+      <c r="H54" t="n">
+        <v>110.8086824417114</v>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>trained</t>
+        </is>
+      </c>
+      <c r="J54" t="n">
+        <v>48168</v>
+      </c>
+      <c r="K54" t="n">
+        <v>38534</v>
+      </c>
+      <c r="L54" t="n">
+        <v>9634</v>
+      </c>
+      <c r="M54" t="n">
+        <v>126.779096364975</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>LSTM</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>attention_lstm</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>v5_no_fuel_and_cost</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>-0.181812047958374</v>
+      </c>
+      <c r="E55" t="n">
+        <v>353.1080932617188</v>
+      </c>
+      <c r="F55" t="n">
+        <v>297128.125</v>
+      </c>
+      <c r="G55" t="n">
+        <v>545.0946044921875</v>
+      </c>
+      <c r="H55" t="n">
+        <v>83.90169143676758</v>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>trained</t>
+        </is>
+      </c>
+      <c r="J55" t="n">
+        <v>48168</v>
+      </c>
+      <c r="K55" t="n">
+        <v>38534</v>
+      </c>
+      <c r="L55" t="n">
+        <v>9634</v>
+      </c>
+      <c r="M55" t="n">
+        <v>1599.229945898056</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>LSTM</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>lstm_simple</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>v5_no_fuel_and_cost_lags</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>-0.1810719966888428</v>
+      </c>
+      <c r="E56" t="n">
+        <v>353.1339111328125</v>
+      </c>
+      <c r="F56" t="n">
+        <v>297095.46875</v>
+      </c>
+      <c r="G56" t="n">
+        <v>545.0646362304688</v>
+      </c>
+      <c r="H56" t="n">
+        <v>84.01034474372864</v>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>trained</t>
+        </is>
+      </c>
+      <c r="J56" t="n">
+        <v>48144</v>
+      </c>
+      <c r="K56" t="n">
+        <v>38515</v>
+      </c>
+      <c r="L56" t="n">
+        <v>9629</v>
+      </c>
+      <c r="M56" t="n">
+        <v>652.3104157447815</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>LSTM</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>lstm_deep</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>v5_no_fuel_and_cost_lags</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>-0.1782864332199097</v>
+      </c>
+      <c r="E57" t="n">
+        <v>352.9871826171875</v>
+      </c>
+      <c r="F57" t="n">
+        <v>296394.78125</v>
+      </c>
+      <c r="G57" t="n">
+        <v>544.4215087890625</v>
+      </c>
+      <c r="H57" t="n">
+        <v>84.40302014350891</v>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>trained</t>
+        </is>
+      </c>
+      <c r="J57" t="n">
+        <v>48144</v>
+      </c>
+      <c r="K57" t="n">
+        <v>38515</v>
+      </c>
+      <c r="L57" t="n">
+        <v>9629</v>
+      </c>
+      <c r="M57" t="n">
+        <v>12660.41068696976</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>LSTM</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>lstm_bidirectional</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>v5_no_fuel_and_cost_lags</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>-0.08275437355041504</v>
+      </c>
+      <c r="E58" t="n">
+        <v>326.5052795410156</v>
+      </c>
+      <c r="F58" t="n">
+        <v>272363.9375</v>
+      </c>
+      <c r="G58" t="n">
+        <v>521.885009765625</v>
+      </c>
+      <c r="H58" t="n">
+        <v>86.04952096939087</v>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>trained</t>
+        </is>
+      </c>
+      <c r="J58" t="n">
+        <v>48144</v>
+      </c>
+      <c r="K58" t="n">
+        <v>38515</v>
+      </c>
+      <c r="L58" t="n">
+        <v>9629</v>
+      </c>
+      <c r="M58" t="n">
+        <v>957.4274113178253</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>LSTM</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>bilstm_stacked</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>v5_no_fuel_and_cost_lags</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>-0.1791723966598511</v>
+      </c>
+      <c r="E59" t="n">
+        <v>353.0338439941406</v>
+      </c>
+      <c r="F59" t="n">
+        <v>296617.625</v>
+      </c>
+      <c r="G59" t="n">
+        <v>544.6261596679688</v>
+      </c>
+      <c r="H59" t="n">
+        <v>84.27786231040955</v>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>trained</t>
+        </is>
+      </c>
+      <c r="J59" t="n">
+        <v>48144</v>
+      </c>
+      <c r="K59" t="n">
+        <v>38515</v>
+      </c>
+      <c r="L59" t="n">
+        <v>9629</v>
+      </c>
+      <c r="M59" t="n">
+        <v>3112.905826091766</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>LSTM</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>cnn_lstm</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>v5_no_fuel_and_cost_lags</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>0.8675240874290466</v>
+      </c>
+      <c r="E60" t="n">
+        <v>89.83045196533203</v>
+      </c>
+      <c r="F60" t="n">
+        <v>33323.9609375</v>
+      </c>
+      <c r="G60" t="n">
+        <v>182.5485229492188</v>
+      </c>
+      <c r="H60" t="n">
+        <v>157.5546383857727</v>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>trained</t>
+        </is>
+      </c>
+      <c r="J60" t="n">
+        <v>48144</v>
+      </c>
+      <c r="K60" t="n">
+        <v>38515</v>
+      </c>
+      <c r="L60" t="n">
+        <v>9629</v>
+      </c>
+      <c r="M60" t="n">
+        <v>170.6583096981049</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>LSTM</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>attention_lstm</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>v5_no_fuel_and_cost_lags</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>-0.1805572509765625</v>
+      </c>
+      <c r="E61" t="n">
+        <v>353.1068115234375</v>
+      </c>
+      <c r="F61" t="n">
+        <v>296965.96875</v>
+      </c>
+      <c r="G61" t="n">
+        <v>544.9458618164062</v>
+      </c>
+      <c r="H61" t="n">
+        <v>84.08267498016357</v>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>trained</t>
+        </is>
+      </c>
+      <c r="J61" t="n">
+        <v>48144</v>
+      </c>
+      <c r="K61" t="n">
+        <v>38515</v>
+      </c>
+      <c r="L61" t="n">
+        <v>9629</v>
+      </c>
+      <c r="M61" t="n">
+        <v>1745.48637342453</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>LSTM</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>lstm_simple</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>v6_no_econ_fuel_cost</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>-0.1831142902374268</v>
+      </c>
+      <c r="E62" t="n">
+        <v>353.1776123046875</v>
+      </c>
+      <c r="F62" t="n">
+        <v>297455.53125</v>
+      </c>
+      <c r="G62" t="n">
+        <v>545.3948364257812</v>
+      </c>
+      <c r="H62" t="n">
+        <v>83.71999859809875</v>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>trained</t>
+        </is>
+      </c>
+      <c r="J62" t="n">
+        <v>48168</v>
+      </c>
+      <c r="K62" t="n">
+        <v>38534</v>
+      </c>
+      <c r="L62" t="n">
+        <v>9634</v>
+      </c>
+      <c r="M62" t="n">
+        <v>615.4547498226166</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>LSTM</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>lstm_deep</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>v6_no_econ_fuel_cost</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>-0.1788188219070435</v>
+      </c>
+      <c r="E63" t="n">
+        <v>352.9496459960938</v>
+      </c>
+      <c r="F63" t="n">
+        <v>296375.5625</v>
+      </c>
+      <c r="G63" t="n">
+        <v>544.4038696289062</v>
+      </c>
+      <c r="H63" t="n">
+        <v>84.32286381721497</v>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>trained</t>
+        </is>
+      </c>
+      <c r="J63" t="n">
+        <v>48168</v>
+      </c>
+      <c r="K63" t="n">
+        <v>38534</v>
+      </c>
+      <c r="L63" t="n">
+        <v>9634</v>
+      </c>
+      <c r="M63" t="n">
+        <v>2835.78316116333</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>LSTM</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>lstm_bidirectional</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>v6_no_econ_fuel_cost</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>-0.1975433826446533</v>
+      </c>
+      <c r="E64" t="n">
+        <v>353.7079467773438</v>
+      </c>
+      <c r="F64" t="n">
+        <v>301083.25</v>
+      </c>
+      <c r="G64" t="n">
+        <v>548.7105102539062</v>
+      </c>
+      <c r="H64" t="n">
+        <v>81.86137676239014</v>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>trained</t>
+        </is>
+      </c>
+      <c r="J64" t="n">
+        <v>48168</v>
+      </c>
+      <c r="K64" t="n">
+        <v>38534</v>
+      </c>
+      <c r="L64" t="n">
+        <v>9634</v>
+      </c>
+      <c r="M64" t="n">
+        <v>1072.199736595154</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>LSTM</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>bilstm_stacked</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>v6_no_econ_fuel_cost</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>-0.1764153242111206</v>
+      </c>
+      <c r="E65" t="n">
+        <v>352.8226013183594</v>
+      </c>
+      <c r="F65" t="n">
+        <v>295771.28125</v>
+      </c>
+      <c r="G65" t="n">
+        <v>543.8485717773438</v>
+      </c>
+      <c r="H65" t="n">
+        <v>84.66377854347229</v>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>trained</t>
+        </is>
+      </c>
+      <c r="J65" t="n">
+        <v>48168</v>
+      </c>
+      <c r="K65" t="n">
+        <v>38534</v>
+      </c>
+      <c r="L65" t="n">
+        <v>9634</v>
+      </c>
+      <c r="M65" t="n">
+        <v>3240.772629261017</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>LSTM</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>cnn_lstm</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>v6_no_econ_fuel_cost</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>0.3415599465370178</v>
+      </c>
+      <c r="E66" t="n">
+        <v>232.368408203125</v>
+      </c>
+      <c r="F66" t="n">
+        <v>165543.28125</v>
+      </c>
+      <c r="G66" t="n">
+        <v>406.8701171875</v>
+      </c>
+      <c r="H66" t="n">
+        <v>102.8270959854126</v>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>trained</t>
+        </is>
+      </c>
+      <c r="J66" t="n">
+        <v>48168</v>
+      </c>
+      <c r="K66" t="n">
+        <v>38534</v>
+      </c>
+      <c r="L66" t="n">
+        <v>9634</v>
+      </c>
+      <c r="M66" t="n">
+        <v>125.7254605293274</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>LSTM</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>attention_lstm</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>v6_no_econ_fuel_cost</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>-0.1807422637939453</v>
+      </c>
+      <c r="E67" t="n">
+        <v>353.0514526367188</v>
+      </c>
+      <c r="F67" t="n">
+        <v>296859.15625</v>
+      </c>
+      <c r="G67" t="n">
+        <v>544.8478393554688</v>
+      </c>
+      <c r="H67" t="n">
+        <v>84.05159115791321</v>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>trained</t>
+        </is>
+      </c>
+      <c r="J67" t="n">
+        <v>48168</v>
+      </c>
+      <c r="K67" t="n">
+        <v>38534</v>
+      </c>
+      <c r="L67" t="n">
+        <v>9634</v>
+      </c>
+      <c r="M67" t="n">
+        <v>1620.364972114563</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>LSTM</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>lstm_simple</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>v6_no_econ_fuel_cost_lags</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>-0.1815787553787231</v>
+      </c>
+      <c r="E68" t="n">
+        <v>353.16064453125</v>
+      </c>
+      <c r="F68" t="n">
+        <v>297222.9375</v>
+      </c>
+      <c r="G68" t="n">
+        <v>545.1815795898438</v>
+      </c>
+      <c r="H68" t="n">
+        <v>83.93912315368652</v>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>trained</t>
+        </is>
+      </c>
+      <c r="J68" t="n">
+        <v>48144</v>
+      </c>
+      <c r="K68" t="n">
+        <v>38515</v>
+      </c>
+      <c r="L68" t="n">
+        <v>9629</v>
+      </c>
+      <c r="M68" t="n">
+        <v>650.6815800666809</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>LSTM</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>lstm_deep</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>v6_no_econ_fuel_cost_lags</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>-0.1795579195022583</v>
+      </c>
+      <c r="E69" t="n">
+        <v>353.0540771484375</v>
+      </c>
+      <c r="F69" t="n">
+        <v>296714.59375</v>
+      </c>
+      <c r="G69" t="n">
+        <v>544.7151489257812</v>
+      </c>
+      <c r="H69" t="n">
+        <v>84.22318696975708</v>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>trained</t>
+        </is>
+      </c>
+      <c r="J69" t="n">
+        <v>48144</v>
+      </c>
+      <c r="K69" t="n">
+        <v>38515</v>
+      </c>
+      <c r="L69" t="n">
+        <v>9629</v>
+      </c>
+      <c r="M69" t="n">
+        <v>2918.681483030319</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>LSTM</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>lstm_bidirectional</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>v6_no_econ_fuel_cost_lags</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>-0.1799426078796387</v>
+      </c>
+      <c r="E70" t="n">
+        <v>353.0743408203125</v>
+      </c>
+      <c r="F70" t="n">
+        <v>296811.34375</v>
+      </c>
+      <c r="G70" t="n">
+        <v>544.803955078125</v>
+      </c>
+      <c r="H70" t="n">
+        <v>84.16911959648132</v>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>trained</t>
+        </is>
+      </c>
+      <c r="J70" t="n">
+        <v>48144</v>
+      </c>
+      <c r="K70" t="n">
+        <v>38515</v>
+      </c>
+      <c r="L70" t="n">
+        <v>9629</v>
+      </c>
+      <c r="M70" t="n">
+        <v>1093.476599216461</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>LSTM</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>bilstm_stacked</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>v6_no_econ_fuel_cost_lags</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>-0.1775758266448975</v>
+      </c>
+      <c r="E71" t="n">
+        <v>352.9496459960938</v>
+      </c>
+      <c r="F71" t="n">
+        <v>296216</v>
+      </c>
+      <c r="G71" t="n">
+        <v>544.2572631835938</v>
+      </c>
+      <c r="H71" t="n">
+        <v>84.50427055358887</v>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>trained</t>
+        </is>
+      </c>
+      <c r="J71" t="n">
+        <v>48144</v>
+      </c>
+      <c r="K71" t="n">
+        <v>38515</v>
+      </c>
+      <c r="L71" t="n">
+        <v>9629</v>
+      </c>
+      <c r="M71" t="n">
+        <v>3252.694169998169</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>LSTM</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>cnn_lstm</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>v6_no_econ_fuel_cost_lags</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>0.8747869729995728</v>
+      </c>
+      <c r="E72" t="n">
+        <v>87.32535552978516</v>
+      </c>
+      <c r="F72" t="n">
+        <v>31496.9921875</v>
+      </c>
+      <c r="G72" t="n">
+        <v>177.4739227294922</v>
+      </c>
+      <c r="H72" t="n">
+        <v>169.6436047554016</v>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>trained</t>
+        </is>
+      </c>
+      <c r="J72" t="n">
+        <v>48144</v>
+      </c>
+      <c r="K72" t="n">
+        <v>38515</v>
+      </c>
+      <c r="L72" t="n">
+        <v>9629</v>
+      </c>
+      <c r="M72" t="n">
+        <v>140.1363391876221</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>LSTM</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>attention_lstm</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>v6_no_econ_fuel_cost_lags</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>-0.1816343069076538</v>
+      </c>
+      <c r="E73" t="n">
+        <v>353.16357421875</v>
+      </c>
+      <c r="F73" t="n">
+        <v>297236.9375</v>
+      </c>
+      <c r="G73" t="n">
+        <v>545.1943969726562</v>
+      </c>
+      <c r="H73" t="n">
+        <v>83.93133282661438</v>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>trained</t>
+        </is>
+      </c>
+      <c r="J73" t="n">
+        <v>48144</v>
+      </c>
+      <c r="K73" t="n">
+        <v>38515</v>
+      </c>
+      <c r="L73" t="n">
+        <v>9629</v>
+      </c>
+      <c r="M73" t="n">
+        <v>1627.401809930801</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>LSTM</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>lstm_simple</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>v7_only_gen_enso</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>0.2564065456390381</v>
+      </c>
+      <c r="E74" t="n">
+        <v>241.0625152587891</v>
+      </c>
+      <c r="F74" t="n">
+        <v>186952.328125</v>
+      </c>
+      <c r="G74" t="n">
+        <v>432.3798522949219</v>
+      </c>
+      <c r="H74" t="n">
+        <v>106.7173361778259</v>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>trained</t>
+        </is>
+      </c>
+      <c r="J74" t="n">
+        <v>48168</v>
+      </c>
+      <c r="K74" t="n">
+        <v>38534</v>
+      </c>
+      <c r="L74" t="n">
+        <v>9634</v>
+      </c>
+      <c r="M74" t="n">
+        <v>611.7214994430542</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>LSTM</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>lstm_deep</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>v7_only_gen_enso</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>0.2952702045440674</v>
+      </c>
+      <c r="E75" t="n">
+        <v>239.924072265625</v>
+      </c>
+      <c r="F75" t="n">
+        <v>177181.34375</v>
+      </c>
+      <c r="G75" t="n">
+        <v>420.9291381835938</v>
+      </c>
+      <c r="H75" t="n">
+        <v>103.547465801239</v>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>trained</t>
+        </is>
+      </c>
+      <c r="J75" t="n">
+        <v>48168</v>
+      </c>
+      <c r="K75" t="n">
+        <v>38534</v>
+      </c>
+      <c r="L75" t="n">
+        <v>9634</v>
+      </c>
+      <c r="M75" t="n">
+        <v>2115.106155872345</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>LSTM</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>lstm_bidirectional</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>v7_only_gen_enso</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>0.4504339098930359</v>
+      </c>
+      <c r="E76" t="n">
+        <v>215.6415252685547</v>
+      </c>
+      <c r="F76" t="n">
+        <v>138170.46875</v>
+      </c>
+      <c r="G76" t="n">
+        <v>371.712890625</v>
+      </c>
+      <c r="H76" t="n">
+        <v>131.8435549736023</v>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>trained</t>
+        </is>
+      </c>
+      <c r="J76" t="n">
+        <v>48168</v>
+      </c>
+      <c r="K76" t="n">
+        <v>38534</v>
+      </c>
+      <c r="L76" t="n">
+        <v>9634</v>
+      </c>
+      <c r="M76" t="n">
+        <v>374.5165541172028</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>LSTM</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>bilstm_stacked</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>v7_only_gen_enso</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>0.2507455348968506</v>
+      </c>
+      <c r="E77" t="n">
+        <v>243.0849914550781</v>
+      </c>
+      <c r="F77" t="n">
+        <v>188375.609375</v>
+      </c>
+      <c r="G77" t="n">
+        <v>434.0225830078125</v>
+      </c>
+      <c r="H77" t="n">
+        <v>103.4568309783936</v>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>trained</t>
+        </is>
+      </c>
+      <c r="J77" t="n">
+        <v>48168</v>
+      </c>
+      <c r="K77" t="n">
+        <v>38534</v>
+      </c>
+      <c r="L77" t="n">
+        <v>9634</v>
+      </c>
+      <c r="M77" t="n">
+        <v>2132.573152780533</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>LSTM</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>cnn_lstm</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>v7_only_gen_enso</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>0.3347684741020203</v>
+      </c>
+      <c r="E78" t="n">
+        <v>301.7859802246094</v>
+      </c>
+      <c r="F78" t="n">
+        <v>167250.78125</v>
+      </c>
+      <c r="G78" t="n">
+        <v>408.9630432128906</v>
+      </c>
+      <c r="H78" t="n">
+        <v>209.0163707733154</v>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>trained</t>
+        </is>
+      </c>
+      <c r="J78" t="n">
+        <v>48168</v>
+      </c>
+      <c r="K78" t="n">
+        <v>38534</v>
+      </c>
+      <c r="L78" t="n">
+        <v>9634</v>
+      </c>
+      <c r="M78" t="n">
+        <v>126.1737303733826</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>LSTM</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>attention_lstm</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>v7_only_gen_enso</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>0.02901458740234375</v>
+      </c>
+      <c r="E79" t="n">
+        <v>289.8162231445312</v>
+      </c>
+      <c r="F79" t="n">
+        <v>244122.625</v>
+      </c>
+      <c r="G79" t="n">
+        <v>494.0876770019531</v>
+      </c>
+      <c r="H79" t="n">
+        <v>102.1058917045593</v>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>trained</t>
+        </is>
+      </c>
+      <c r="J79" t="n">
+        <v>48168</v>
+      </c>
+      <c r="K79" t="n">
+        <v>38534</v>
+      </c>
+      <c r="L79" t="n">
+        <v>9634</v>
+      </c>
+      <c r="M79" t="n">
+        <v>1649.980437040329</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>LSTM</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>lstm_simple</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>v7_only_gen_enso_lags</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>0.414418637752533</v>
+      </c>
+      <c r="E80" t="n">
+        <v>215.4032135009766</v>
+      </c>
+      <c r="F80" t="n">
+        <v>147225.34375</v>
+      </c>
+      <c r="G80" t="n">
+        <v>383.6995544433594</v>
+      </c>
+      <c r="H80" t="n">
+        <v>118.9135789871216</v>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>trained</t>
+        </is>
+      </c>
+      <c r="J80" t="n">
+        <v>48168</v>
+      </c>
+      <c r="K80" t="n">
+        <v>38534</v>
+      </c>
+      <c r="L80" t="n">
+        <v>9634</v>
+      </c>
+      <c r="M80" t="n">
+        <v>640.9997818470001</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>LSTM</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>lstm_deep</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>v7_only_gen_enso_lags</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>0.4167916178703308</v>
+      </c>
+      <c r="E81" t="n">
+        <v>200.0982971191406</v>
+      </c>
+      <c r="F81" t="n">
+        <v>146628.734375</v>
+      </c>
+      <c r="G81" t="n">
+        <v>382.9213256835938</v>
+      </c>
+      <c r="H81" t="n">
+        <v>127.4271368980408</v>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>trained</t>
+        </is>
+      </c>
+      <c r="J81" t="n">
+        <v>48168</v>
+      </c>
+      <c r="K81" t="n">
+        <v>38534</v>
+      </c>
+      <c r="L81" t="n">
+        <v>9634</v>
+      </c>
+      <c r="M81" t="n">
+        <v>2182.503380298615</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>LSTM</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>lstm_bidirectional</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>v7_only_gen_enso_lags</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>0.3843563199043274</v>
+      </c>
+      <c r="E82" t="n">
+        <v>207.5311126708984</v>
+      </c>
+      <c r="F82" t="n">
+        <v>154783.546875</v>
+      </c>
+      <c r="G82" t="n">
+        <v>393.4254150390625</v>
+      </c>
+      <c r="H82" t="n">
+        <v>118.8586473464966</v>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>trained</t>
+        </is>
+      </c>
+      <c r="J82" t="n">
+        <v>48168</v>
+      </c>
+      <c r="K82" t="n">
+        <v>38534</v>
+      </c>
+      <c r="L82" t="n">
+        <v>9634</v>
+      </c>
+      <c r="M82" t="n">
+        <v>402.0475850105286</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>LSTM</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>bilstm_stacked</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>v7_only_gen_enso_lags</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>0.5132306218147278</v>
+      </c>
+      <c r="E83" t="n">
+        <v>194.1158905029297</v>
+      </c>
+      <c r="F83" t="n">
+        <v>122382.296875</v>
+      </c>
+      <c r="G83" t="n">
+        <v>349.8318176269531</v>
+      </c>
+      <c r="H83" t="n">
+        <v>130.8598041534424</v>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>trained</t>
+        </is>
+      </c>
+      <c r="J83" t="n">
+        <v>48168</v>
+      </c>
+      <c r="K83" t="n">
+        <v>38534</v>
+      </c>
+      <c r="L83" t="n">
+        <v>9634</v>
+      </c>
+      <c r="M83" t="n">
+        <v>1354.973567247391</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>LSTM</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>cnn_lstm</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>v7_only_gen_enso_lags</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>0.3649945855140686</v>
+      </c>
+      <c r="E84" t="n">
+        <v>284.0499267578125</v>
+      </c>
+      <c r="F84" t="n">
+        <v>159651.40625</v>
+      </c>
+      <c r="G84" t="n">
+        <v>399.5640258789062</v>
+      </c>
+      <c r="H84" t="n">
+        <v>194.4573283195496</v>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>trained</t>
+        </is>
+      </c>
+      <c r="J84" t="n">
+        <v>48168</v>
+      </c>
+      <c r="K84" t="n">
+        <v>38534</v>
+      </c>
+      <c r="L84" t="n">
+        <v>9634</v>
+      </c>
+      <c r="M84" t="n">
+        <v>75.84991908073425</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>LSTM</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>attention_lstm</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>v7_only_gen_enso_lags</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>0.3859822750091553</v>
+      </c>
+      <c r="E85" t="n">
+        <v>219.5863037109375</v>
+      </c>
+      <c r="F85" t="n">
+        <v>154374.75</v>
+      </c>
+      <c r="G85" t="n">
+        <v>392.905517578125</v>
+      </c>
+      <c r="H85" t="n">
+        <v>124.4572520256042</v>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>trained</t>
+        </is>
+      </c>
+      <c r="J85" t="n">
+        <v>48168</v>
+      </c>
+      <c r="K85" t="n">
+        <v>38534</v>
+      </c>
+      <c r="L85" t="n">
+        <v>9634</v>
+      </c>
+      <c r="M85" t="n">
+        <v>1534.174232721329</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>LSTM</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>lstm_simple</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>v8_only_gen_no_solar_enso</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>0.2916733026504517</v>
+      </c>
+      <c r="E86" t="n">
+        <v>236.5290069580078</v>
+      </c>
+      <c r="F86" t="n">
+        <v>178085.65625</v>
+      </c>
+      <c r="G86" t="n">
+        <v>422.001953125</v>
+      </c>
+      <c r="H86" t="n">
+        <v>115.1285529136658</v>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>trained</t>
+        </is>
+      </c>
+      <c r="J86" t="n">
+        <v>48168</v>
+      </c>
+      <c r="K86" t="n">
+        <v>38534</v>
+      </c>
+      <c r="L86" t="n">
+        <v>9634</v>
+      </c>
+      <c r="M86" t="n">
+        <v>645.7883939743042</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>LSTM</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>lstm_deep</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>v8_only_gen_no_solar_enso</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>0.4167991876602173</v>
+      </c>
+      <c r="E87" t="n">
+        <v>224.6289215087891</v>
+      </c>
+      <c r="F87" t="n">
+        <v>146626.828125</v>
+      </c>
+      <c r="G87" t="n">
+        <v>382.9188232421875</v>
+      </c>
+      <c r="H87" t="n">
+        <v>115.1849508285522</v>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>trained</t>
+        </is>
+      </c>
+      <c r="J87" t="n">
+        <v>48168</v>
+      </c>
+      <c r="K87" t="n">
+        <v>38534</v>
+      </c>
+      <c r="L87" t="n">
+        <v>9634</v>
+      </c>
+      <c r="M87" t="n">
+        <v>3008.874991416931</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>LSTM</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>lstm_bidirectional</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>v8_only_gen_no_solar_enso</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>0.4255394339561462</v>
+      </c>
+      <c r="E88" t="n">
+        <v>205.2019348144531</v>
+      </c>
+      <c r="F88" t="n">
+        <v>144429.390625</v>
+      </c>
+      <c r="G88" t="n">
+        <v>380.0386657714844</v>
+      </c>
+      <c r="H88" t="n">
+        <v>120.0070261955261</v>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>trained</t>
+        </is>
+      </c>
+      <c r="J88" t="n">
+        <v>48168</v>
+      </c>
+      <c r="K88" t="n">
+        <v>38534</v>
+      </c>
+      <c r="L88" t="n">
+        <v>9634</v>
+      </c>
+      <c r="M88" t="n">
+        <v>1142.198692083359</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>LSTM</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>bilstm_stacked</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>v8_only_gen_no_solar_enso</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>0.5338659286499023</v>
+      </c>
+      <c r="E89" t="n">
+        <v>184.1870574951172</v>
+      </c>
+      <c r="F89" t="n">
+        <v>117194.21875</v>
+      </c>
+      <c r="G89" t="n">
+        <v>342.33642578125</v>
+      </c>
+      <c r="H89" t="n">
+        <v>134.4788908958435</v>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>trained</t>
+        </is>
+      </c>
+      <c r="J89" t="n">
+        <v>48168</v>
+      </c>
+      <c r="K89" t="n">
+        <v>38534</v>
+      </c>
+      <c r="L89" t="n">
+        <v>9634</v>
+      </c>
+      <c r="M89" t="n">
+        <v>3536.754039287567</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>LSTM</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>cnn_lstm</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>v8_only_gen_no_solar_enso</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>0.4135028719902039</v>
+      </c>
+      <c r="E90" t="n">
+        <v>233.2530670166016</v>
+      </c>
+      <c r="F90" t="n">
+        <v>147455.59375</v>
+      </c>
+      <c r="G90" t="n">
+        <v>383.9994812011719</v>
+      </c>
+      <c r="H90" t="n">
+        <v>152.9585480690002</v>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>trained</t>
+        </is>
+      </c>
+      <c r="J90" t="n">
+        <v>48168</v>
+      </c>
+      <c r="K90" t="n">
+        <v>38534</v>
+      </c>
+      <c r="L90" t="n">
+        <v>9634</v>
+      </c>
+      <c r="M90" t="n">
+        <v>133.8836042881012</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>LSTM</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>attention_lstm</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>v8_only_gen_no_solar_enso</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>0.1871327757835388</v>
+      </c>
+      <c r="E91" t="n">
+        <v>274.8209533691406</v>
+      </c>
+      <c r="F91" t="n">
+        <v>204368.96875</v>
+      </c>
+      <c r="G91" t="n">
+        <v>452.0718688964844</v>
+      </c>
+      <c r="H91" t="n">
+        <v>117.2081351280212</v>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>trained</t>
+        </is>
+      </c>
+      <c r="J91" t="n">
+        <v>48168</v>
+      </c>
+      <c r="K91" t="n">
+        <v>38534</v>
+      </c>
+      <c r="L91" t="n">
+        <v>9634</v>
+      </c>
+      <c r="M91" t="n">
+        <v>1821.620107889175</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>LSTM</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>lstm_simple</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>v8_only_gen_no_solar_enso_lags</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>0.4085407853126526</v>
+      </c>
+      <c r="E92" t="n">
+        <v>208.2016296386719</v>
+      </c>
+      <c r="F92" t="n">
+        <v>148703.140625</v>
+      </c>
+      <c r="G92" t="n">
+        <v>385.6204528808594</v>
+      </c>
+      <c r="H92" t="n">
+        <v>112.9990220069885</v>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>trained</t>
+        </is>
+      </c>
+      <c r="J92" t="n">
+        <v>48168</v>
+      </c>
+      <c r="K92" t="n">
+        <v>38534</v>
+      </c>
+      <c r="L92" t="n">
+        <v>9634</v>
+      </c>
+      <c r="M92" t="n">
+        <v>719.7310078144073</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>LSTM</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>lstm_deep</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>v8_only_gen_no_solar_enso_lags</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>0.4579741358757019</v>
+      </c>
+      <c r="E93" t="n">
+        <v>205.3511199951172</v>
+      </c>
+      <c r="F93" t="n">
+        <v>136274.734375</v>
+      </c>
+      <c r="G93" t="n">
+        <v>369.1540832519531</v>
+      </c>
+      <c r="H93" t="n">
+        <v>120.8537340164185</v>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>trained</t>
+        </is>
+      </c>
+      <c r="J93" t="n">
+        <v>48168</v>
+      </c>
+      <c r="K93" t="n">
+        <v>38534</v>
+      </c>
+      <c r="L93" t="n">
+        <v>9634</v>
+      </c>
+      <c r="M93" t="n">
+        <v>1508.487183094025</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>LSTM</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>lstm_bidirectional</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>v8_only_gen_no_solar_enso_lags</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>0.3615233302116394</v>
+      </c>
+      <c r="E94" t="n">
+        <v>234.7135620117188</v>
+      </c>
+      <c r="F94" t="n">
+        <v>160524.140625</v>
+      </c>
+      <c r="G94" t="n">
+        <v>400.6546325683594</v>
+      </c>
+      <c r="H94" t="n">
+        <v>122.6903080940247</v>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>trained</t>
+        </is>
+      </c>
+      <c r="J94" t="n">
+        <v>48168</v>
+      </c>
+      <c r="K94" t="n">
+        <v>38534</v>
+      </c>
+      <c r="L94" t="n">
+        <v>9634</v>
+      </c>
+      <c r="M94" t="n">
+        <v>1117.883423566818</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>LSTM</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>bilstm_stacked</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>v8_only_gen_no_solar_enso_lags</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>0.4256765842437744</v>
+      </c>
+      <c r="E95" t="n">
+        <v>213.4186096191406</v>
+      </c>
+      <c r="F95" t="n">
+        <v>144394.90625</v>
+      </c>
+      <c r="G95" t="n">
+        <v>379.9932861328125</v>
+      </c>
+      <c r="H95" t="n">
+        <v>118.3539628982544</v>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>trained</t>
+        </is>
+      </c>
+      <c r="J95" t="n">
+        <v>48168</v>
+      </c>
+      <c r="K95" t="n">
+        <v>38534</v>
+      </c>
+      <c r="L95" t="n">
+        <v>9634</v>
+      </c>
+      <c r="M95" t="n">
+        <v>3497.459895372391</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>LSTM</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>cnn_lstm</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>v8_only_gen_no_solar_enso_lags</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>0.2832081913948059</v>
+      </c>
+      <c r="E96" t="n">
+        <v>325.4257202148438</v>
+      </c>
+      <c r="F96" t="n">
+        <v>180213.921875</v>
+      </c>
+      <c r="G96" t="n">
+        <v>424.51611328125</v>
+      </c>
+      <c r="H96" t="n">
+        <v>223.665976524353</v>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>trained</t>
+        </is>
+      </c>
+      <c r="J96" t="n">
+        <v>48168</v>
+      </c>
+      <c r="K96" t="n">
+        <v>38534</v>
+      </c>
+      <c r="L96" t="n">
+        <v>9634</v>
+      </c>
+      <c r="M96" t="n">
+        <v>133.2382228374481</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>LSTM</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>attention_lstm</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>v8_only_gen_no_solar_enso_lags</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>0.3604562282562256</v>
+      </c>
+      <c r="E97" t="n">
+        <v>223.2144165039062</v>
+      </c>
+      <c r="F97" t="n">
+        <v>160792.4375</v>
+      </c>
+      <c r="G97" t="n">
+        <v>400.9893188476562</v>
+      </c>
+      <c r="H97" t="n">
+        <v>122.0117688179016</v>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>trained</t>
+        </is>
+      </c>
+      <c r="J97" t="n">
+        <v>48168</v>
+      </c>
+      <c r="K97" t="n">
+        <v>38534</v>
+      </c>
+      <c r="L97" t="n">
+        <v>9634</v>
+      </c>
+      <c r="M97" t="n">
+        <v>1748.450975894928</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>LSTM</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>lstm_simple</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>v9_date_range_all</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>-1.595366477966309</v>
+      </c>
+      <c r="E98" t="n">
+        <v>148.5909423828125</v>
+      </c>
+      <c r="F98" t="n">
+        <v>25036.89453125</v>
+      </c>
+      <c r="G98" t="n">
+        <v>158.2305145263672</v>
+      </c>
+      <c r="H98" t="n">
+        <v>121.5832948684692</v>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>trained</t>
+        </is>
+      </c>
+      <c r="J98" t="n">
+        <v>13081</v>
+      </c>
+      <c r="K98" t="n">
+        <v>10464</v>
+      </c>
+      <c r="L98" t="n">
+        <v>2617</v>
+      </c>
+      <c r="M98" t="n">
+        <v>169.6631886959076</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>LSTM</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>lstm_deep</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>v9_date_range_all</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>-16.11999893188477</v>
+      </c>
+      <c r="E99" t="n">
+        <v>399.6730346679688</v>
+      </c>
+      <c r="F99" t="n">
+        <v>165152.640625</v>
+      </c>
+      <c r="G99" t="n">
+        <v>406.3897705078125</v>
+      </c>
+      <c r="H99" t="n">
+        <v>335.1274728775024</v>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>trained</t>
+        </is>
+      </c>
+      <c r="J99" t="n">
+        <v>13081</v>
+      </c>
+      <c r="K99" t="n">
+        <v>10464</v>
+      </c>
+      <c r="L99" t="n">
+        <v>2617</v>
+      </c>
+      <c r="M99" t="n">
+        <v>851.3756635189056</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>LSTM</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>lstm_bidirectional</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>v9_date_range_all</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>-14.51717662811279</v>
+      </c>
+      <c r="E100" t="n">
+        <v>379.9803161621094</v>
+      </c>
+      <c r="F100" t="n">
+        <v>149690.578125</v>
+      </c>
+      <c r="G100" t="n">
+        <v>386.898681640625</v>
+      </c>
+      <c r="H100" t="n">
+        <v>318.9925193786621</v>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>trained</t>
+        </is>
+      </c>
+      <c r="J100" t="n">
+        <v>13081</v>
+      </c>
+      <c r="K100" t="n">
+        <v>10464</v>
+      </c>
+      <c r="L100" t="n">
+        <v>2617</v>
+      </c>
+      <c r="M100" t="n">
+        <v>282.7712345123291</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>LSTM</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>bilstm_stacked</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>v9_date_range_all</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>-24.95634078979492</v>
+      </c>
+      <c r="E101" t="n">
+        <v>494.4591064453125</v>
+      </c>
+      <c r="F101" t="n">
+        <v>250394.75</v>
+      </c>
+      <c r="G101" t="n">
+        <v>500.3945922851562</v>
+      </c>
+      <c r="H101" t="n">
+        <v>412.4692916870117</v>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>trained</t>
+        </is>
+      </c>
+      <c r="J101" t="n">
+        <v>13081</v>
+      </c>
+      <c r="K101" t="n">
+        <v>10464</v>
+      </c>
+      <c r="L101" t="n">
+        <v>2617</v>
+      </c>
+      <c r="M101" t="n">
+        <v>934.4822471141815</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>LSTM</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>cnn_lstm</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>v9_date_range_all</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>-0.7037191390991211</v>
+      </c>
+      <c r="E102" t="n">
+        <v>101.1181488037109</v>
+      </c>
+      <c r="F102" t="n">
+        <v>16435.380859375</v>
+      </c>
+      <c r="G102" t="n">
+        <v>128.2005462646484</v>
+      </c>
+      <c r="H102" t="n">
+        <v>96.70373201370239</v>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>trained</t>
+        </is>
+      </c>
+      <c r="J102" t="n">
+        <v>13081</v>
+      </c>
+      <c r="K102" t="n">
+        <v>10464</v>
+      </c>
+      <c r="L102" t="n">
+        <v>2617</v>
+      </c>
+      <c r="M102" t="n">
+        <v>41.65855979919434</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>LSTM</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>attention_lstm</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>v9_date_range_all</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>-23.19800186157227</v>
+      </c>
+      <c r="E103" t="n">
+        <v>477.1264953613281</v>
+      </c>
+      <c r="F103" t="n">
+        <v>233432.484375</v>
+      </c>
+      <c r="G103" t="n">
+        <v>483.1484985351562</v>
+      </c>
+      <c r="H103" t="n">
+        <v>398.3346223831177</v>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>trained</t>
+        </is>
+      </c>
+      <c r="J103" t="n">
+        <v>13081</v>
+      </c>
+      <c r="K103" t="n">
+        <v>10464</v>
+      </c>
+      <c r="L103" t="n">
+        <v>2617</v>
+      </c>
+      <c r="M103" t="n">
+        <v>432.7067520618439</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>LSTM</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>lstm_simple</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>v9_date_range_all_lags</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>-0.5559672117233276</v>
+      </c>
+      <c r="E104" t="n">
+        <v>105.8896179199219</v>
+      </c>
+      <c r="F104" t="n">
+        <v>15035.029296875</v>
+      </c>
+      <c r="G104" t="n">
+        <v>122.6174087524414</v>
+      </c>
+      <c r="H104" t="n">
+        <v>82.91228413581848</v>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>trained</t>
+        </is>
+      </c>
+      <c r="J104" t="n">
+        <v>13057</v>
+      </c>
+      <c r="K104" t="n">
+        <v>10445</v>
+      </c>
+      <c r="L104" t="n">
+        <v>2612</v>
+      </c>
+      <c r="M104" t="n">
+        <v>199.8927850723267</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>LSTM</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>lstm_deep</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>v9_date_range_all_lags</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>-16.04633522033691</v>
+      </c>
+      <c r="E105" t="n">
+        <v>399.1195068359375</v>
+      </c>
+      <c r="F105" t="n">
+        <v>164715.640625</v>
+      </c>
+      <c r="G105" t="n">
+        <v>405.8517456054688</v>
+      </c>
+      <c r="H105" t="n">
+        <v>334.8604679107666</v>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>trained</t>
+        </is>
+      </c>
+      <c r="J105" t="n">
+        <v>13057</v>
+      </c>
+      <c r="K105" t="n">
+        <v>10445</v>
+      </c>
+      <c r="L105" t="n">
+        <v>2612</v>
+      </c>
+      <c r="M105" t="n">
+        <v>864.6523084640503</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>LSTM</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>lstm_bidirectional</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>v9_date_range_all_lags</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>-22.76803016662598</v>
+      </c>
+      <c r="E106" t="n">
+        <v>473.1849060058594</v>
+      </c>
+      <c r="F106" t="n">
+        <v>229666.15625</v>
+      </c>
+      <c r="G106" t="n">
+        <v>479.2349548339844</v>
+      </c>
+      <c r="H106" t="n">
+        <v>395.3389883041382</v>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>trained</t>
+        </is>
+      </c>
+      <c r="J106" t="n">
+        <v>13057</v>
+      </c>
+      <c r="K106" t="n">
+        <v>10445</v>
+      </c>
+      <c r="L106" t="n">
+        <v>2612</v>
+      </c>
+      <c r="M106" t="n">
+        <v>364.9511494636536</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>LSTM</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>bilstm_stacked</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>v9_date_range_all_lags</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>-23.81089210510254</v>
+      </c>
+      <c r="E107" t="n">
+        <v>483.6359252929688</v>
+      </c>
+      <c r="F107" t="n">
+        <v>239743.140625</v>
+      </c>
+      <c r="G107" t="n">
+        <v>489.6357116699219</v>
+      </c>
+      <c r="H107" t="n">
+        <v>403.8722038269043</v>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>trained</t>
+        </is>
+      </c>
+      <c r="J107" t="n">
+        <v>13057</v>
+      </c>
+      <c r="K107" t="n">
+        <v>10445</v>
+      </c>
+      <c r="L107" t="n">
+        <v>2612</v>
+      </c>
+      <c r="M107" t="n">
+        <v>661.08904337883</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>LSTM</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>cnn_lstm</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>v9_date_range_all_lags</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>0.3289648294448853</v>
+      </c>
+      <c r="E108" t="n">
+        <v>47.18814468383789</v>
+      </c>
+      <c r="F108" t="n">
+        <v>6484.09130859375</v>
+      </c>
+      <c r="G108" t="n">
+        <v>80.52385711669922</v>
+      </c>
+      <c r="H108" t="n">
+        <v>46.32995426654816</v>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>trained</t>
+        </is>
+      </c>
+      <c r="J108" t="n">
+        <v>13057</v>
+      </c>
+      <c r="K108" t="n">
+        <v>10445</v>
+      </c>
+      <c r="L108" t="n">
+        <v>2612</v>
+      </c>
+      <c r="M108" t="n">
+        <v>26.46738600730896</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>LSTM</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>attention_lstm</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>v9_date_range_all_lags</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>-17.40496635437012</v>
+      </c>
+      <c r="E109" t="n">
+        <v>415.1864929199219</v>
+      </c>
+      <c r="F109" t="n">
+        <v>177843.84375</v>
+      </c>
+      <c r="G109" t="n">
+        <v>421.7153625488281</v>
+      </c>
+      <c r="H109" t="n">
+        <v>347.9809284210205</v>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>trained</t>
+        </is>
+      </c>
+      <c r="J109" t="n">
+        <v>13057</v>
+      </c>
+      <c r="K109" t="n">
+        <v>10445</v>
+      </c>
+      <c r="L109" t="n">
+        <v>2612</v>
+      </c>
+      <c r="M109" t="n">
+        <v>269.3900294303894</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>LSTM</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>lstm_simple</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>v10_date_range_no_solar</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>-0.6419185400009155</v>
+      </c>
+      <c r="E110" t="n">
+        <v>110.3174438476562</v>
+      </c>
+      <c r="F110" t="n">
+        <v>15839.205078125</v>
+      </c>
+      <c r="G110" t="n">
+        <v>125.8539047241211</v>
+      </c>
+      <c r="H110" t="n">
+        <v>86.94565296173096</v>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>trained</t>
+        </is>
+      </c>
+      <c r="J110" t="n">
+        <v>13081</v>
+      </c>
+      <c r="K110" t="n">
+        <v>10464</v>
+      </c>
+      <c r="L110" t="n">
+        <v>2617</v>
+      </c>
+      <c r="M110" t="n">
+        <v>78.86212563514709</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>LSTM</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>lstm_deep</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>v10_date_range_no_solar</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>-16.07832908630371</v>
+      </c>
+      <c r="E111" t="n">
+        <v>399.1719665527344</v>
+      </c>
+      <c r="F111" t="n">
+        <v>164750.65625</v>
+      </c>
+      <c r="G111" t="n">
+        <v>405.8948974609375</v>
+      </c>
+      <c r="H111" t="n">
+        <v>334.7179174423218</v>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>trained</t>
+        </is>
+      </c>
+      <c r="J111" t="n">
+        <v>13081</v>
+      </c>
+      <c r="K111" t="n">
+        <v>10464</v>
+      </c>
+      <c r="L111" t="n">
+        <v>2617</v>
+      </c>
+      <c r="M111" t="n">
+        <v>358.9495244026184</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>LSTM</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>lstm_bidirectional</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>v10_date_range_no_solar</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>-12.51981353759766</v>
+      </c>
+      <c r="E112" t="n">
+        <v>354.0083923339844</v>
+      </c>
+      <c r="F112" t="n">
+        <v>130422.484375</v>
+      </c>
+      <c r="G112" t="n">
+        <v>361.1405334472656</v>
+      </c>
+      <c r="H112" t="n">
+        <v>297.6126670837402</v>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>trained</t>
+        </is>
+      </c>
+      <c r="J112" t="n">
+        <v>13081</v>
+      </c>
+      <c r="K112" t="n">
+        <v>10464</v>
+      </c>
+      <c r="L112" t="n">
+        <v>2617</v>
+      </c>
+      <c r="M112" t="n">
+        <v>100.3517224788666</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>LSTM</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>bilstm_stacked</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>v10_date_range_no_solar</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>-23.36578750610352</v>
+      </c>
+      <c r="E113" t="n">
+        <v>478.8067321777344</v>
+      </c>
+      <c r="F113" t="n">
+        <v>235051.0625</v>
+      </c>
+      <c r="G113" t="n">
+        <v>484.8206481933594</v>
+      </c>
+      <c r="H113" t="n">
+        <v>399.7057199478149</v>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>trained</t>
+        </is>
+      </c>
+      <c r="J113" t="n">
+        <v>13081</v>
+      </c>
+      <c r="K113" t="n">
+        <v>10464</v>
+      </c>
+      <c r="L113" t="n">
+        <v>2617</v>
+      </c>
+      <c r="M113" t="n">
+        <v>376.2464029788971</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>LSTM</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>cnn_lstm</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>v10_date_range_no_solar</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>-2.093223571777344</v>
+      </c>
+      <c r="E114" t="n">
+        <v>159.4615478515625</v>
+      </c>
+      <c r="F114" t="n">
+        <v>29839.60546875</v>
+      </c>
+      <c r="G114" t="n">
+        <v>172.7414398193359</v>
+      </c>
+      <c r="H114" t="n">
+        <v>141.2041306495667</v>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>trained</t>
+        </is>
+      </c>
+      <c r="J114" t="n">
+        <v>13081</v>
+      </c>
+      <c r="K114" t="n">
+        <v>10464</v>
+      </c>
+      <c r="L114" t="n">
+        <v>2617</v>
+      </c>
+      <c r="M114" t="n">
+        <v>23.28153419494629</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>LSTM</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>attention_lstm</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>v10_date_range_no_solar</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>-16.48730659484863</v>
+      </c>
+      <c r="E115" t="n">
+        <v>404.0679321289062</v>
+      </c>
+      <c r="F115" t="n">
+        <v>168695.96875</v>
+      </c>
+      <c r="G115" t="n">
+        <v>410.7261352539062</v>
+      </c>
+      <c r="H115" t="n">
+        <v>338.7143611907959</v>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>trained</t>
+        </is>
+      </c>
+      <c r="J115" t="n">
+        <v>13081</v>
+      </c>
+      <c r="K115" t="n">
+        <v>10464</v>
+      </c>
+      <c r="L115" t="n">
+        <v>2617</v>
+      </c>
+      <c r="M115" t="n">
+        <v>203.7625226974487</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>LSTM</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>lstm_simple</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
           <t>v10_date_range_no_solar_lags</t>
         </is>
       </c>
-      <c r="D7" t="n">
-        <v>-22.45830535888672</v>
-      </c>
-      <c r="E7" t="n">
-        <v>470.0351867675781</v>
-      </c>
-      <c r="F7" t="n">
-        <v>226673.34375</v>
-      </c>
-      <c r="G7" t="n">
-        <v>476.1022338867188</v>
-      </c>
-      <c r="H7" t="n">
-        <v>392.7669763565063</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>trained</t>
-        </is>
-      </c>
-      <c r="J7" t="n">
+      <c r="D116" t="n">
+        <v>-0.8057522773742676</v>
+      </c>
+      <c r="E116" t="n">
+        <v>118.3591461181641</v>
+      </c>
+      <c r="F116" t="n">
+        <v>17448.65625</v>
+      </c>
+      <c r="G116" t="n">
+        <v>132.0933685302734</v>
+      </c>
+      <c r="H116" t="n">
+        <v>94.27338838577271</v>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>trained</t>
+        </is>
+      </c>
+      <c r="J116" t="n">
         <v>13057</v>
       </c>
-      <c r="K7" t="n">
+      <c r="K116" t="n">
         <v>10445</v>
       </c>
-      <c r="L7" t="n">
+      <c r="L116" t="n">
         <v>2612</v>
       </c>
-      <c r="M7" t="n">
-        <v>246.2220530509949</v>
+      <c r="M116" t="n">
+        <v>92.87820935249329</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>LSTM</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>lstm_deep</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>v10_date_range_no_solar_lags</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>-16.06335639953613</v>
+      </c>
+      <c r="E117" t="n">
+        <v>399.32470703125</v>
+      </c>
+      <c r="F117" t="n">
+        <v>164880.125</v>
+      </c>
+      <c r="G117" t="n">
+        <v>406.0543518066406</v>
+      </c>
+      <c r="H117" t="n">
+        <v>335.0283145904541</v>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>trained</t>
+        </is>
+      </c>
+      <c r="J117" t="n">
+        <v>13057</v>
+      </c>
+      <c r="K117" t="n">
+        <v>10445</v>
+      </c>
+      <c r="L117" t="n">
+        <v>2612</v>
+      </c>
+      <c r="M117" t="n">
+        <v>382.968585729599</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>LSTM</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>lstm_bidirectional</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>v10_date_range_no_solar_lags</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>-12.60211372375488</v>
+      </c>
+      <c r="E118" t="n">
+        <v>355.4123229980469</v>
+      </c>
+      <c r="F118" t="n">
+        <v>131434.75</v>
+      </c>
+      <c r="G118" t="n">
+        <v>362.539306640625</v>
+      </c>
+      <c r="H118" t="n">
+        <v>298.9327192306519</v>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>trained</t>
+        </is>
+      </c>
+      <c r="J118" t="n">
+        <v>13057</v>
+      </c>
+      <c r="K118" t="n">
+        <v>10445</v>
+      </c>
+      <c r="L118" t="n">
+        <v>2612</v>
+      </c>
+      <c r="M118" t="n">
+        <v>117.8609142303467</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>LSTM</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>bilstm_stacked</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>v10_date_range_no_solar_lags</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>-24.88648414611816</v>
+      </c>
+      <c r="E119" t="n">
+        <v>494.1916198730469</v>
+      </c>
+      <c r="F119" t="n">
+        <v>250136.40625</v>
+      </c>
+      <c r="G119" t="n">
+        <v>500.1363830566406</v>
+      </c>
+      <c r="H119" t="n">
+        <v>412.4821662902832</v>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>trained</t>
+        </is>
+      </c>
+      <c r="J119" t="n">
+        <v>13057</v>
+      </c>
+      <c r="K119" t="n">
+        <v>10445</v>
+      </c>
+      <c r="L119" t="n">
+        <v>2612</v>
+      </c>
+      <c r="M119" t="n">
+        <v>383.6120462417603</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>LSTM</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>cnn_lstm</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>v10_date_range_no_solar_lags</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>0.322087824344635</v>
+      </c>
+      <c r="E120" t="n">
+        <v>45.59077453613281</v>
+      </c>
+      <c r="F120" t="n">
+        <v>6550.5419921875</v>
+      </c>
+      <c r="G120" t="n">
+        <v>80.93541717529297</v>
+      </c>
+      <c r="H120" t="n">
+        <v>43.45763921737671</v>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>trained</t>
+        </is>
+      </c>
+      <c r="J120" t="n">
+        <v>13057</v>
+      </c>
+      <c r="K120" t="n">
+        <v>10445</v>
+      </c>
+      <c r="L120" t="n">
+        <v>2612</v>
+      </c>
+      <c r="M120" t="n">
+        <v>24.69045734405518</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>LSTM</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>attention_lstm</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>v10_date_range_no_solar_lags</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>-15.21078300476074</v>
+      </c>
+      <c r="E121" t="n">
+        <v>388.9289245605469</v>
+      </c>
+      <c r="F121" t="n">
+        <v>156641.859375</v>
+      </c>
+      <c r="G121" t="n">
+        <v>395.7800598144531</v>
+      </c>
+      <c r="H121" t="n">
+        <v>326.5198469161987</v>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>trained</t>
+        </is>
+      </c>
+      <c r="J121" t="n">
+        <v>13057</v>
+      </c>
+      <c r="K121" t="n">
+        <v>10445</v>
+      </c>
+      <c r="L121" t="n">
+        <v>2612</v>
+      </c>
+      <c r="M121" t="n">
+        <v>218.9441802501678</v>
       </c>
     </row>
   </sheetData>
